--- a/planilhas/Copa do Brasil.xlsx
+++ b/planilhas/Copa do Brasil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kleberson\Desktop\meu-site - Copia\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8766AF-A4CA-4BA9-BD47-D6B18A98B111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7980532-8F82-4921-9A84-A55188B1E9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4F49A5ED-3A92-472E-8FA7-25B42F4FCE77}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="141">
   <si>
     <t>IDA</t>
   </si>
@@ -917,6 +917,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -957,9 +960,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1168,7 +1168,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>53</xdr:col>
-      <xdr:colOff>602831</xdr:colOff>
+      <xdr:colOff>602830</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>231321</xdr:rowOff>
     </xdr:to>
@@ -1375,7 +1375,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>99</xdr:col>
-      <xdr:colOff>479424</xdr:colOff>
+      <xdr:colOff>479425</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>231321</xdr:rowOff>
     </xdr:to>
@@ -1880,12 +1880,12 @@
   <sheetFormatPr defaultColWidth="7.5703125" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="4.28515625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1930,7 +1930,7 @@
     <col min="55" max="56" width="4.28515625" style="3" customWidth="1"/>
     <col min="57" max="57" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.85546875" style="3" customWidth="1"/>
-    <col min="59" max="59" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="5.42578125" style="3" customWidth="1"/>
     <col min="60" max="60" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="61" max="62" width="4.28515625" style="3" customWidth="1"/>
     <col min="63" max="63" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -1941,7 +1941,7 @@
     <col min="69" max="69" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="39.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="73" max="74" width="4.28515625" style="3" customWidth="1"/>
     <col min="75" max="75" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="76" max="76" width="8.85546875" style="4" bestFit="1" customWidth="1"/>
@@ -2196,89 +2196,89 @@
       <c r="CS14" s="1"/>
     </row>
     <row r="15" spans="2:97" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="H15" s="40" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="H15" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="N15" s="48" t="s">
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="N15" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="T15" s="44" t="s">
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="T15" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="Z15" s="46" t="s">
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="Z15" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="47"/>
-      <c r="AF15" s="52" t="s">
+      <c r="AA15" s="48"/>
+      <c r="AB15" s="48"/>
+      <c r="AC15" s="48"/>
+      <c r="AF15" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="AG15" s="53"/>
-      <c r="AH15" s="53"/>
-      <c r="AI15" s="53"/>
-      <c r="AL15" s="42" t="s">
+      <c r="AG15" s="54"/>
+      <c r="AH15" s="54"/>
+      <c r="AI15" s="54"/>
+      <c r="AL15" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="43"/>
-      <c r="AS15" s="52" t="s">
+      <c r="AM15" s="44"/>
+      <c r="AN15" s="44"/>
+      <c r="AO15" s="44"/>
+      <c r="AP15" s="44"/>
+      <c r="AS15" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="AT15" s="53"/>
-      <c r="AU15" s="53"/>
-      <c r="AV15" s="53"/>
-      <c r="AY15" s="46" t="s">
+      <c r="AT15" s="54"/>
+      <c r="AU15" s="54"/>
+      <c r="AV15" s="54"/>
+      <c r="AY15" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="AZ15" s="47"/>
-      <c r="BA15" s="47"/>
-      <c r="BB15" s="47"/>
-      <c r="BE15" s="50" t="s">
+      <c r="AZ15" s="48"/>
+      <c r="BA15" s="48"/>
+      <c r="BB15" s="48"/>
+      <c r="BE15" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="BF15" s="51"/>
-      <c r="BG15" s="51"/>
-      <c r="BH15" s="51"/>
+      <c r="BF15" s="52"/>
+      <c r="BG15" s="52"/>
+      <c r="BH15" s="52"/>
       <c r="BI15" s="7"/>
       <c r="BJ15" s="7"/>
-      <c r="BK15" s="48" t="s">
+      <c r="BK15" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="BL15" s="49"/>
-      <c r="BM15" s="49"/>
-      <c r="BN15" s="49"/>
+      <c r="BL15" s="50"/>
+      <c r="BM15" s="50"/>
+      <c r="BN15" s="50"/>
       <c r="BO15" s="31"/>
-      <c r="BQ15" s="40" t="s">
+      <c r="BQ15" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="BR15" s="40"/>
-      <c r="BS15" s="40"/>
-      <c r="BT15" s="40"/>
+      <c r="BR15" s="41"/>
+      <c r="BS15" s="41"/>
+      <c r="BT15" s="41"/>
       <c r="BU15" s="31"/>
-      <c r="BW15" s="41" t="s">
+      <c r="BW15" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="BX15" s="41"/>
-      <c r="BY15" s="41"/>
-      <c r="BZ15" s="41"/>
+      <c r="BX15" s="42"/>
+      <c r="BY15" s="42"/>
+      <c r="BZ15" s="42"/>
       <c r="CC15" s="3"/>
       <c r="CD15" s="3"/>
       <c r="CE15" s="3"/>
@@ -2297,63 +2297,63 @@
       <c r="CS15" s="1"/>
     </row>
     <row r="16" spans="2:97" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="45"/>
-      <c r="V16" s="45"/>
-      <c r="W16" s="45"/>
-      <c r="Z16" s="47"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="47"/>
-      <c r="AC16" s="47"/>
-      <c r="AF16" s="53"/>
-      <c r="AG16" s="53"/>
-      <c r="AH16" s="53"/>
-      <c r="AI16" s="53"/>
-      <c r="AL16" s="43"/>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43"/>
-      <c r="AP16" s="43"/>
-      <c r="AS16" s="53"/>
-      <c r="AT16" s="53"/>
-      <c r="AU16" s="53"/>
-      <c r="AV16" s="53"/>
-      <c r="AY16" s="47"/>
-      <c r="AZ16" s="47"/>
-      <c r="BA16" s="47"/>
-      <c r="BB16" s="47"/>
-      <c r="BE16" s="51"/>
-      <c r="BF16" s="51"/>
-      <c r="BG16" s="51"/>
-      <c r="BH16" s="51"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="Z16" s="48"/>
+      <c r="AA16" s="48"/>
+      <c r="AB16" s="48"/>
+      <c r="AC16" s="48"/>
+      <c r="AF16" s="54"/>
+      <c r="AG16" s="54"/>
+      <c r="AH16" s="54"/>
+      <c r="AI16" s="54"/>
+      <c r="AL16" s="44"/>
+      <c r="AM16" s="44"/>
+      <c r="AN16" s="44"/>
+      <c r="AO16" s="44"/>
+      <c r="AP16" s="44"/>
+      <c r="AS16" s="54"/>
+      <c r="AT16" s="54"/>
+      <c r="AU16" s="54"/>
+      <c r="AV16" s="54"/>
+      <c r="AY16" s="48"/>
+      <c r="AZ16" s="48"/>
+      <c r="BA16" s="48"/>
+      <c r="BB16" s="48"/>
+      <c r="BE16" s="52"/>
+      <c r="BF16" s="52"/>
+      <c r="BG16" s="52"/>
+      <c r="BH16" s="52"/>
       <c r="BI16" s="7"/>
       <c r="BJ16" s="7"/>
-      <c r="BK16" s="49"/>
-      <c r="BL16" s="49"/>
-      <c r="BM16" s="49"/>
-      <c r="BN16" s="49"/>
+      <c r="BK16" s="50"/>
+      <c r="BL16" s="50"/>
+      <c r="BM16" s="50"/>
+      <c r="BN16" s="50"/>
       <c r="BO16" s="31"/>
-      <c r="BQ16" s="40"/>
-      <c r="BR16" s="40"/>
-      <c r="BS16" s="40"/>
-      <c r="BT16" s="40"/>
+      <c r="BQ16" s="41"/>
+      <c r="BR16" s="41"/>
+      <c r="BS16" s="41"/>
+      <c r="BT16" s="41"/>
       <c r="BU16" s="31"/>
-      <c r="BW16" s="41"/>
-      <c r="BX16" s="41"/>
-      <c r="BY16" s="41"/>
-      <c r="BZ16" s="41"/>
+      <c r="BW16" s="42"/>
+      <c r="BX16" s="42"/>
+      <c r="BY16" s="42"/>
+      <c r="BZ16" s="42"/>
       <c r="CC16" s="3"/>
       <c r="CD16" s="3"/>
       <c r="CE16" s="3"/>
@@ -2574,7 +2574,9 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="H20" s="8"/>
+      <c r="H20" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="I20" s="9">
         <v>0</v>
       </c>
@@ -2626,7 +2628,9 @@
       <c r="BS20" s="10">
         <v>0</v>
       </c>
-      <c r="BT20" s="10"/>
+      <c r="BT20" s="10" t="s">
+        <v>16</v>
+      </c>
       <c r="BU20" s="32"/>
       <c r="CC20" s="3"/>
       <c r="CD20" s="3"/>
@@ -2657,7 +2661,9 @@
         <v>6</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="H21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>130</v>
+      </c>
       <c r="I21" s="14">
         <v>0</v>
       </c>
@@ -2711,7 +2717,9 @@
       <c r="BS21" s="15">
         <v>0</v>
       </c>
-      <c r="BT21" s="15"/>
+      <c r="BT21" s="15" t="s">
+        <v>136</v>
+      </c>
       <c r="BU21" s="32"/>
       <c r="BW21" s="4" t="s">
         <v>6</v>
@@ -3379,7 +3387,9 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="H28" s="8"/>
+      <c r="H28" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="I28" s="9">
         <v>0</v>
       </c>
@@ -3441,7 +3451,9 @@
       <c r="BS28" s="10">
         <v>0</v>
       </c>
-      <c r="BT28" s="10"/>
+      <c r="BT28" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="BU28" s="32"/>
       <c r="CC28" s="3"/>
       <c r="CD28" s="3"/>
@@ -3472,7 +3484,9 @@
         <v>6</v>
       </c>
       <c r="F29" s="4"/>
-      <c r="H29" s="13"/>
+      <c r="H29" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="I29" s="14">
         <v>0</v>
       </c>
@@ -3532,7 +3546,9 @@
       <c r="BS29" s="15">
         <v>0</v>
       </c>
-      <c r="BT29" s="15"/>
+      <c r="BT29" s="15" t="s">
+        <v>69</v>
+      </c>
       <c r="BU29" s="32"/>
       <c r="BW29" s="4" t="s">
         <v>6</v>
@@ -4016,7 +4032,9 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="H36" s="8"/>
+      <c r="H36" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="I36" s="9">
         <v>0</v>
       </c>
@@ -4068,7 +4086,9 @@
       <c r="BS36" s="10">
         <v>0</v>
       </c>
-      <c r="BT36" s="10"/>
+      <c r="BT36" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="BU36" s="32"/>
       <c r="CC36" s="3"/>
       <c r="CD36" s="3"/>
@@ -4087,7 +4107,9 @@
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="21"/>
-      <c r="H37" s="13"/>
+      <c r="H37" s="13" t="s">
+        <v>72</v>
+      </c>
       <c r="I37" s="14">
         <v>0</v>
       </c>
@@ -4141,7 +4163,9 @@
       <c r="BS37" s="15">
         <v>0</v>
       </c>
-      <c r="BT37" s="15"/>
+      <c r="BT37" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="BU37" s="32"/>
       <c r="BW37" s="4" t="s">
         <v>6</v>
@@ -4731,7 +4755,9 @@
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="H44" s="8"/>
+      <c r="H44" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="I44" s="9">
         <v>0</v>
       </c>
@@ -4793,7 +4819,9 @@
       <c r="BS44" s="10">
         <v>0</v>
       </c>
-      <c r="BT44" s="10"/>
+      <c r="BT44" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="BU44" s="32"/>
       <c r="CC44" s="3"/>
       <c r="CD44" s="3"/>
@@ -4812,7 +4840,9 @@
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="21"/>
-      <c r="H45" s="13"/>
+      <c r="H45" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="I45" s="14">
         <v>0</v>
       </c>
@@ -4872,7 +4902,9 @@
       <c r="BS45" s="15">
         <v>0</v>
       </c>
-      <c r="BT45" s="15"/>
+      <c r="BT45" s="15" t="s">
+        <v>76</v>
+      </c>
       <c r="BU45" s="32"/>
       <c r="BW45" s="4" t="s">
         <v>6</v>
@@ -5098,8 +5130,8 @@
       <c r="AN49" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AO49" s="54"/>
-      <c r="AP49" s="54"/>
+      <c r="AO49" s="40"/>
+      <c r="AP49" s="40"/>
       <c r="AS49" s="12">
         <f>AU49+AT49</f>
         <v>0</v>
@@ -5250,7 +5282,9 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="H52" s="8"/>
+      <c r="H52" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="I52" s="9">
         <v>0</v>
       </c>
@@ -5275,7 +5309,9 @@
       <c r="BS52" s="10">
         <v>0</v>
       </c>
-      <c r="BT52" s="10"/>
+      <c r="BT52" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="BU52" s="32"/>
       <c r="CC52" s="3"/>
       <c r="CD52" s="3"/>
@@ -5294,7 +5330,9 @@
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="21"/>
-      <c r="H53" s="13"/>
+      <c r="H53" s="13" t="s">
+        <v>10</v>
+      </c>
       <c r="I53" s="14">
         <v>0</v>
       </c>
@@ -5321,7 +5359,9 @@
       <c r="BS53" s="15">
         <v>0</v>
       </c>
-      <c r="BT53" s="15"/>
+      <c r="BT53" s="15" t="s">
+        <v>99</v>
+      </c>
       <c r="BU53" s="32"/>
       <c r="BW53" s="4" t="s">
         <v>6</v>
@@ -5737,7 +5777,9 @@
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="H60" s="8"/>
+      <c r="H60" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I60" s="9">
         <v>0</v>
       </c>
@@ -5774,7 +5816,9 @@
       <c r="BS60" s="10">
         <v>0</v>
       </c>
-      <c r="BT60" s="10"/>
+      <c r="BT60" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="BU60" s="32"/>
       <c r="CC60" s="3"/>
       <c r="CD60" s="3"/>
@@ -5793,7 +5837,9 @@
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="21"/>
-      <c r="H61" s="13"/>
+      <c r="H61" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="I61" s="14">
         <v>0</v>
       </c>
@@ -5828,7 +5874,9 @@
       <c r="BS61" s="15">
         <v>0</v>
       </c>
-      <c r="BT61" s="15"/>
+      <c r="BT61" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="BU61" s="32"/>
       <c r="BW61" s="4" t="s">
         <v>6</v>
@@ -6177,7 +6225,9 @@
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="H68" s="8"/>
+      <c r="H68" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="I68" s="9">
         <v>0</v>
       </c>
@@ -6206,7 +6256,9 @@
       <c r="BS68" s="10">
         <v>0</v>
       </c>
-      <c r="BT68" s="10"/>
+      <c r="BT68" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="BU68" s="32"/>
       <c r="CC68" s="3"/>
       <c r="CD68" s="3"/>
@@ -6224,7 +6276,9 @@
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="21"/>
-      <c r="H69" s="13"/>
+      <c r="H69" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="I69" s="14">
         <v>0</v>
       </c>
@@ -6255,7 +6309,9 @@
       <c r="BS69" s="15">
         <v>0</v>
       </c>
-      <c r="BT69" s="15"/>
+      <c r="BT69" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="BU69" s="32"/>
       <c r="BW69" s="4" t="s">
         <v>6</v>
@@ -6653,7 +6709,9 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="H76" s="8"/>
+      <c r="H76" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="I76" s="9">
         <v>0</v>
       </c>
@@ -6678,7 +6736,9 @@
       <c r="BS76" s="10">
         <v>0</v>
       </c>
-      <c r="BT76" s="10"/>
+      <c r="BT76" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="BU76" s="32"/>
       <c r="CC76" s="3"/>
       <c r="CD76" s="3"/>
@@ -6697,7 +6757,9 @@
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="21"/>
-      <c r="H77" s="13"/>
+      <c r="H77" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="I77" s="14">
         <v>0</v>
       </c>
@@ -6720,7 +6782,9 @@
       <c r="BS77" s="15">
         <v>0</v>
       </c>
-      <c r="BT77" s="15"/>
+      <c r="BT77" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="BU77" s="32"/>
       <c r="BW77" s="4" t="s">
         <v>6</v>
